--- a/resources/Intro to R_Codebücher.xlsx
+++ b/resources/Intro to R_Codebücher.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neikos/Documents/work/Teaching_Seminar Intro R/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neikos/Documents/work/Teaching_Seminar Intro R/Intro_to_R_Seminar/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF0FF6A-330B-4A4E-8451-1B63F339F3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD54EA08-3CB2-6949-8EF1-41B0D1641607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{7EC32914-7440-BB4F-9CFA-119FC8207BDD}"/>
   </bookViews>
@@ -609,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -627,9 +627,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -947,7 +944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8ED7F14-D2C9-E044-A63D-F49119ED59CE}">
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.83203125" style="1" customWidth="1"/>
@@ -977,10 +974,10 @@
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="1" t="s">
         <v>152</v>
       </c>
       <c r="C3" s="3"/>
@@ -1093,549 +1090,538 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="5"/>
-    </row>
-    <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="5"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="5"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="51" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="155" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>163</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="155" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="155" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C23" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="155" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C24" s="2" t="s">
+    <row r="21" spans="1:3" ht="155" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="155" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>58</v>
+        <v>12</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="4" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" s="4" customFormat="1" ht="36" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>14</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="4" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="4" customFormat="1" ht="190" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" s="4" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" s="4" customFormat="1" ht="190" customHeight="1" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="2"/>
+    </row>
+    <row r="37" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="43" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="29" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="43" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="29" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C40" s="2"/>
-    </row>
-    <row r="41" spans="1:3" ht="43" x14ac:dyDescent="0.2">
-      <c r="A41" s="5" t="s">
-        <v>24</v>
+        <v>97</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="29" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A42" s="5" t="s">
-        <v>25</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="29" x14ac:dyDescent="0.2">
-      <c r="A43" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="43" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="29" x14ac:dyDescent="0.2">
-      <c r="A44" s="5" t="s">
-        <v>94</v>
+      <c r="A44" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="29" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="29" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="29" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>144</v>
+        <v>121</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="29" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="43" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="163" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="43" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="168" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="43" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="168" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="43" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="163" customHeight="1" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="168" customHeight="1" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="29" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="168" customHeight="1" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="29" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+      <c r="B59" s="6"/>
+      <c r="C59" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="43" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B63" s="6"/>
-      <c r="C63" s="2" t="s">
-        <v>166</v>
+        <v>148</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="A66" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="A67" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A68" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C68" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C73" s="8"/>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C74" s="8"/>
+    <row r="69" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C69" s="7"/>
+    </row>
+    <row r="70" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C70" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/Intro to R_Codebücher.xlsx
+++ b/resources/Intro to R_Codebücher.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neikos/Documents/work/Teaching_Seminar Intro R/Intro_to_R_Seminar/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD54EA08-3CB2-6949-8EF1-41B0D1641607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8995A87E-2CBD-3740-BC61-726C272E2F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{7EC32914-7440-BB4F-9CFA-119FC8207BDD}"/>
   </bookViews>

--- a/resources/Intro to R_Codebücher.xlsx
+++ b/resources/Intro to R_Codebücher.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neikos/Documents/work/Teaching_Seminar Intro R/Intro_to_R_Seminar/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8995A87E-2CBD-3740-BC61-726C272E2F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA99A60-CFE9-A04F-B8C4-43FE25B9BB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{7EC32914-7440-BB4F-9CFA-119FC8207BDD}"/>
+    <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16940" xr2:uid="{7EC32914-7440-BB4F-9CFA-119FC8207BDD}"/>
   </bookViews>
   <sheets>
     <sheet name="OWID" sheetId="1" r:id="rId1"/>
@@ -311,9 +311,6 @@
     <t>This measures total plastic waste generation prior to management and therefore does not represent the quantity of plastic at risk of polluting waterways, rivers and the ocean environment.</t>
   </si>
   <si>
-    <t>Plastic waste generation</t>
-  </si>
-  <si>
     <t>deaths_in_armed_conflicts</t>
   </si>
   <si>
@@ -366,9 +363,6 @@
   </si>
   <si>
     <t>Learning-adjusted years of schooling among children</t>
-  </si>
-  <si>
-    <t>Learning-adjusted years of schooling](#dod:lays) among children combine the quantity and quality of education into one metric, accounting for the fact that similar durations of schooling can yield different learning outcomes.. Source: World Bank based on methodology in Filmer et al. (2018)</t>
   </si>
   <si>
     <t>girls_in_tertiary</t>
@@ -518,9 +512,6 @@
     <t>Share of respondents who report having contact with a public official in the past 12 months and paying or being asked to pay a bribe. Data from United Nations Office on Drugs and Crime</t>
   </si>
   <si>
-    <t>nnual working hours per person employed</t>
-  </si>
-  <si>
     <t>Regular hours worked by full-time and part-time workers, paid and unpaid overtime, hours worked in additional jobs, and time not worked because of public holidays, annual paid leave, strikes and labour disputes, and other reasons. Data from OECD.</t>
   </si>
   <si>
@@ -540,6 +531,15 @@
   </si>
   <si>
     <t>time_use_*</t>
+  </si>
+  <si>
+    <t>Plastic waste generation, in tonnes</t>
+  </si>
+  <si>
+    <t>annual working hours per person employed</t>
+  </si>
+  <si>
+    <t>Learning-adjusted years of schooling among children combine the quantity and quality of education into one metric, accounting for the fact that similar durations of schooling can yield different learning outcomes. Source: World Bank based on methodology in Filmer et al. (2018)</t>
   </si>
 </sst>
 </file>
@@ -975,10 +975,10 @@
     </row>
     <row r="3" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C3" s="3"/>
     </row>
@@ -1015,13 +1015,13 @@
     </row>
     <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="36" x14ac:dyDescent="0.2">
@@ -1138,26 +1138,26 @@
     </row>
     <row r="19" spans="1:3" ht="155" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="155" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="155" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:3" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.3">
@@ -1344,10 +1344,10 @@
     </row>
     <row r="39" spans="1:3" ht="29" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>93</v>
+        <v>166</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>92</v>
@@ -1355,266 +1355,266 @@
     </row>
     <row r="40" spans="1:3" ht="29" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="29" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="29" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="29" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="C46" s="2" t="s">
-        <v>112</v>
+        <v>168</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="163" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="168" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="168" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B55" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C55" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="29" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="69" spans="3:3" x14ac:dyDescent="0.2">

--- a/resources/Intro to R_Codebücher.xlsx
+++ b/resources/Intro to R_Codebücher.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neikos/Documents/work/Teaching_Seminar Intro R/Intro_to_R_Seminar/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA99A60-CFE9-A04F-B8C4-43FE25B9BB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FDF7EAA-1EAC-744F-BE2B-173F2016AB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16940" xr2:uid="{7EC32914-7440-BB4F-9CFA-119FC8207BDD}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="185">
   <si>
     <t>Variable</t>
   </si>
@@ -540,6 +540,54 @@
   </si>
   <si>
     <t>Learning-adjusted years of schooling among children combine the quantity and quality of education into one metric, accounting for the fact that similar durations of schooling can yield different learning outcomes. Source: World Bank based on methodology in Filmer et al. (2018)</t>
+  </si>
+  <si>
+    <t>gender_wage_gap</t>
+  </si>
+  <si>
+    <t>Gender wage gap</t>
+  </si>
+  <si>
+    <t>Difference between average earnings of men and women, expressed as a percentage of average earnings of men. This data is unadjusted for worker characteristics. The data corresponds to gross hourly earnings and includes both full-time and part-time workers. Source: International Labour Organization (2026)</t>
+  </si>
+  <si>
+    <t>life_satisfaction</t>
+  </si>
+  <si>
+    <t>Self-reported life satisfaction</t>
+  </si>
+  <si>
+    <t>Average of survey responses in the World Happiness Report. The survey question asks respondents their current position on a hypothetical ladder, where the best possible life for them is a 10, and the worst possible life is a 0. The Cantril ladder asks respondents to think of a ladder, with the best possible life for them being a 10 and the worst possible life being a 0. They are then asked to rate their own current lives on that 0 to 10 scale. The rankings are calculated by the World Happiness Report based on nationally representative samples collected by the Gallup World Poll. The score is the average of the three-year survey period, i.e. the year 2025 shows the average of the 2023-2025 survey data. The number of people and countries surveyed varies year to year, but typically more than 100,000 people in over 140 countries participate in the Gallup World Poll each year. The rankings are based entirely on the survey scores, which are weighted by Gallup to make the estimates representative. Source: Wellbeing Research Centre (2026).</t>
+  </si>
+  <si>
+    <t>share_internet_users</t>
+  </si>
+  <si>
+    <t>Share of individuals using the internet within country, in percent</t>
+  </si>
+  <si>
+    <t>Share of women who experienced violence from an intimate partner</t>
+  </si>
+  <si>
+    <t>domestic_violence_women</t>
+  </si>
+  <si>
+    <t>Ever-partnered women aged over 15 years who have been subject to physical or sexual violence by a current or former intimate partner in the last 12 months. An ever-partnered woman is a woman who has had an intimate partner at any time in their life. Source: Data from multiple sources compiled by the UN</t>
+  </si>
+  <si>
+    <t>suicide_rate_*</t>
+  </si>
+  <si>
+    <t>Male / female suicide rate</t>
+  </si>
+  <si>
+    <t>Reported annual death rate from suicide per 100,000 people. Suicide deaths are underreported in many countries due to social stigma and cultural or legal concerns. This data has not been adjusted for underreporting, and comparisons may be affected by differences in measurement. Reported rates are based on the underlying cause of death listed on death certificates. To allow for comparisons between countries and over time, this metric is age-standardized. Source: WHO Mortality Database (2025)</t>
+  </si>
+  <si>
+    <t>maternal_mortality_ratio</t>
+  </si>
+  <si>
+    <t>Estimated number of women who die from maternal conditions per 100,000 live births, based on data from death certificates, large-scale surveys, and statistical modeling. rior to 1985, only reported data are available, which are likely to underestimate the true maternal mortality rate. From 1985, estimates are shown, which aim to adjust for underreporting and misclassification. Source: UN MMEIG (2023) and other sources. he dataset combines three sources: WHO Mortality Database (before 1985), Gapminder (before 1985, if WHO Mortality Database data are unavailable), UN MMEIG (1985 onwards). The WHO Mortality Database and Gapminder contain reported figures from countries, and are likely to underestimate the true maternal mortality figures. The UN MMEIG aims to estimates the true rate, by adjusting for underreporting and misclassification. Sudden jumps in mortality rate in 1985 are a consequence of switching data sources (from reported to estimated figures). For the years between 1950 - 1985 we calculated the maternal mortality ratio and maternal mortality rate based on the number of maternal deaths from the WHO mortality database and live births and female population of reproductive age from the UN WPP. Where the reported maternal deaths in the WHO Mortality Database differed significantly from the estimated figures in the UN MMEIG data, we opted not to include them. Where a data point is attached to a range of years in the Gapminder data set, we used the midpoint of the range. The UN MMEIG data shown (post 1985) is the point estimate - this means there is a 50% chance that the true measure lies above this point, and a 50% chance that the true value lies below this point. We calculated regional aggregates by summing the maternal deaths and live births of all countries in the region and then calculating the MMR based on these figures.</t>
   </si>
 </sst>
 </file>
@@ -1617,11 +1665,65 @@
         <v>164</v>
       </c>
     </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C69" s="7"/>
-    </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C70" s="7"/>
+    <row r="65" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="187" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>184</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/Intro to R_Codebücher.xlsx
+++ b/resources/Intro to R_Codebücher.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neikos/Documents/work/Teaching_Seminar Intro R/Intro_to_R_Seminar/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FDF7EAA-1EAC-744F-BE2B-173F2016AB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998EAF5D-03A7-C749-B45F-BD6350648DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16940" xr2:uid="{7EC32914-7440-BB4F-9CFA-119FC8207BDD}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="200">
   <si>
     <t>Variable</t>
   </si>
@@ -588,6 +588,51 @@
   </si>
   <si>
     <t>Estimated number of women who die from maternal conditions per 100,000 live births, based on data from death certificates, large-scale surveys, and statistical modeling. rior to 1985, only reported data are available, which are likely to underestimate the true maternal mortality rate. From 1985, estimates are shown, which aim to adjust for underreporting and misclassification. Source: UN MMEIG (2023) and other sources. he dataset combines three sources: WHO Mortality Database (before 1985), Gapminder (before 1985, if WHO Mortality Database data are unavailable), UN MMEIG (1985 onwards). The WHO Mortality Database and Gapminder contain reported figures from countries, and are likely to underestimate the true maternal mortality figures. The UN MMEIG aims to estimates the true rate, by adjusting for underreporting and misclassification. Sudden jumps in mortality rate in 1985 are a consequence of switching data sources (from reported to estimated figures). For the years between 1950 - 1985 we calculated the maternal mortality ratio and maternal mortality rate based on the number of maternal deaths from the WHO mortality database and live births and female population of reproductive age from the UN WPP. Where the reported maternal deaths in the WHO Mortality Database differed significantly from the estimated figures in the UN MMEIG data, we opted not to include them. Where a data point is attached to a range of years in the Gapminder data set, we used the midpoint of the range. The UN MMEIG data shown (post 1985) is the point estimate - this means there is a 50% chance that the true measure lies above this point, and a 50% chance that the true value lies below this point. We calculated regional aggregates by summing the maternal deaths and live births of all countries in the region and then calculating the MMR based on these figures.</t>
+  </si>
+  <si>
+    <t>scientific_publications_per_million</t>
+  </si>
+  <si>
+    <t>owid_military_spending.csv</t>
+  </si>
+  <si>
+    <t>median_age</t>
+  </si>
+  <si>
+    <t>median_age_projected</t>
+  </si>
+  <si>
+    <t>lgbt_equality_index</t>
+  </si>
+  <si>
+    <t>homicide_rate</t>
+  </si>
+  <si>
+    <t>Annual articles published in scientific and technical journals per million people</t>
+  </si>
+  <si>
+    <t>Includes physics, biology, chemistry, mathematics, clinical medicine, biomedical research, engineering and technology, and earth and space sciences. Articles are assigned based on the country of the first author's institution. Source: National Science Foundation Science and Engineering Indicators, via World Bank (2026); United Nations Population Division, national statistical offices, and Eurostat, via World Bank (2026)</t>
+  </si>
+  <si>
+    <t>Military spending as a share of GDP</t>
+  </si>
+  <si>
+    <t>Military expenditure divided by gross domestic product, expressed as a percentage. Includes military and civil personnel, operation and maintenance, procurement, military research and development, infrastructure, and aid. Source: Stockholm International Peace Research Institute (2026)</t>
+  </si>
+  <si>
+    <t>The median age is the age that divides the population into two equal halves — half of the population is younger, and half is older. Future projections are based on the UN's medium scenario. Source: UN, World Population Prospects (2024)</t>
+  </si>
+  <si>
+    <t>LGBT+ Legal Equality Index</t>
+  </si>
+  <si>
+    <t>The index captures to which extent LGBT+ people have the same rights as straight and cisgender people. It combines 15 individual policies, such as the legality of same-sex relationships, marriage, and gender marker changes. It ranges from 0 to 100 (most equal). The legal equality index summarizes the current legal status of 16 LGBT+ policies — from the legality of same-sex sexual activity and marriage to hate-crime protections and the right to change legal gender — each weighted by how heavily it counts toward the overall ranking. Source: Equaldex (2026); Population based on various sources (2024)</t>
+  </si>
+  <si>
+    <t>Annual number of deaths from homicide per 100,000 people</t>
+  </si>
+  <si>
+    <t>Intentional homicide requires three elements: one person killing another, intent to kill or seriously injure, and the act was illegal. For example, a person who kills another in self-defence is not considered to have committed an intentional homicide as justifiable homicide in self-defence is not illegal. All killings that meet the criteria listed below are to be considered intentional homicides, irrespective of definitions provided by national legislations or practices. Terrorist killings are included as intentional homicides. Source: United Nations Office on Drugs and Crime (2025)</t>
   </si>
 </sst>
 </file>
@@ -992,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8ED7F14-D2C9-E044-A63D-F49119ED59CE}">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.83203125" style="1" customWidth="1"/>
@@ -1723,6 +1768,66 @@
       </c>
       <c r="C70" s="7" t="s">
         <v>184</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="68" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="68" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/resources/Intro to R_Codebücher.xlsx
+++ b/resources/Intro to R_Codebücher.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neikos/Documents/work/Teaching_Seminar Intro R/Intro_to_R_Seminar/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998EAF5D-03A7-C749-B45F-BD6350648DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9EBA4F5-F11E-8A43-8ED4-19395E16AFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16940" xr2:uid="{7EC32914-7440-BB4F-9CFA-119FC8207BDD}"/>
   </bookViews>
@@ -593,9 +593,6 @@
     <t>scientific_publications_per_million</t>
   </si>
   <si>
-    <t>owid_military_spending.csv</t>
-  </si>
-  <si>
     <t>median_age</t>
   </si>
   <si>
@@ -633,6 +630,9 @@
   </si>
   <si>
     <t>Intentional homicide requires three elements: one person killing another, intent to kill or seriously injure, and the act was illegal. For example, a person who kills another in self-defence is not considered to have committed an intentional homicide as justifiable homicide in self-defence is not illegal. All killings that meet the criteria listed below are to be considered intentional homicides, irrespective of definitions provided by national legislations or practices. Terrorist killings are included as intentional homicides. Source: United Nations Office on Drugs and Crime (2025)</t>
+  </si>
+  <si>
+    <t>military_spending</t>
   </si>
 </sst>
 </file>
@@ -1775,59 +1775,59 @@
         <v>185</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/resources/Intro to R_Codebücher.xlsx
+++ b/resources/Intro to R_Codebücher.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neikos/Documents/work/Teaching_Seminar Intro R/Intro_to_R_Seminar/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9EBA4F5-F11E-8A43-8ED4-19395E16AFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050F1442-0DDB-FF42-A122-C6DAD28031FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16940" xr2:uid="{7EC32914-7440-BB4F-9CFA-119FC8207BDD}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="213">
   <si>
     <t>Variable</t>
   </si>
@@ -209,9 +209,6 @@
   </si>
   <si>
     <t>Source: United Nations Inter-agency Group for Child Mortality Estimation (2025) – with minor processing by Our World in Data</t>
-  </si>
-  <si>
-    <t>Geographic location.</t>
   </si>
   <si>
     <t>Year of observation.</t>
@@ -633,6 +630,48 @@
   </si>
   <si>
     <t>military_spending</t>
+  </si>
+  <si>
+    <t>female_homicide_rate</t>
+  </si>
+  <si>
+    <t>Annual number of intentional homicides where the victim was female, per 100,000 women. Includes all age groups. UNODC collects intentional homicide data from criminal justice systems (law enforcement records) and public health systems (death certificates). Intentional homicide requires three elements: one person killing another, intent to kill or seriously injure, and the act was illegal. For example, a person who kills another in self-defence is not considered to have committed an intentional homicide as justifiable homicide in self-defence is not illegal. All killings that meet the criteria listed below are to be considered intentional homicides, irrespective of definitions provided by national legislations or practices. Terrorist killings are included as intentional homicides. Source: UN, World Population Prospects (2024); United Nations Office on Drugs and Crime (2025)</t>
+  </si>
+  <si>
+    <t>mobility_score</t>
+  </si>
+  <si>
+    <t>n_ai_companies</t>
+  </si>
+  <si>
+    <t>n_ai_patents</t>
+  </si>
+  <si>
+    <t>estimated_ai_investment</t>
+  </si>
+  <si>
+    <t>Sum of countries to which passport holders have easy visa access</t>
+  </si>
+  <si>
+    <t>Per country-year, sums up destination countries for which passport holders from origin country have one of the following available: e-visa, visa on arrival, electronic travel authorization, visa free. Source: Based on data from https://www.passportindex.org, accessed through the repositories https://github.com/imorte/passport-index-data/tree/main and https://github.com/ilyankou/passport-index-dataset.</t>
+  </si>
+  <si>
+    <t>share_top*_pct_inc</t>
+  </si>
+  <si>
+    <t>Share of workers above the *th percentile of the earnings distribution in period t, for people aged 25-55. Source: Global Repository of Income Dynamics (GRID)</t>
+  </si>
+  <si>
+    <t>Number of AI-related patents issued in 2025.</t>
+  </si>
+  <si>
+    <t>Estimated AI-related investment in 2025.</t>
+  </si>
+  <si>
+    <t>Number of companies producing AI products in 2025.</t>
+  </si>
+  <si>
+    <t>Geographic location</t>
   </si>
 </sst>
 </file>
@@ -1037,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8ED7F14-D2C9-E044-A63D-F49119ED59CE}">
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.83203125" style="1" customWidth="1"/>
@@ -1062,16 +1101,16 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>212</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="C3" s="3"/>
     </row>
@@ -1080,7 +1119,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -1108,13 +1147,13 @@
     </row>
     <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="36" x14ac:dyDescent="0.2">
@@ -1231,26 +1270,26 @@
     </row>
     <row r="19" spans="1:3" ht="155" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="155" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="155" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:3" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.3">
@@ -1269,10 +1308,10 @@
         <v>9</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
@@ -1280,10 +1319,10 @@
         <v>10</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
@@ -1291,10 +1330,10 @@
         <v>11</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
@@ -1302,10 +1341,10 @@
         <v>12</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:3" s="4" customFormat="1" ht="36" x14ac:dyDescent="0.3">
@@ -1313,10 +1352,10 @@
         <v>13</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
@@ -1324,10 +1363,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
@@ -1335,10 +1374,10 @@
         <v>15</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
@@ -1346,10 +1385,10 @@
         <v>16</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:3" s="4" customFormat="1" ht="24" x14ac:dyDescent="0.3">
@@ -1357,10 +1396,10 @@
         <v>17</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:3" s="4" customFormat="1" ht="36" x14ac:dyDescent="0.3">
@@ -1368,10 +1407,10 @@
         <v>18</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:3" s="4" customFormat="1" ht="190" customHeight="1" x14ac:dyDescent="0.3">
@@ -1379,10 +1418,10 @@
         <v>19</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="18" x14ac:dyDescent="0.2">
@@ -1390,7 +1429,7 @@
         <v>20</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="43" x14ac:dyDescent="0.2">
@@ -1398,10 +1437,10 @@
         <v>21</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="43" x14ac:dyDescent="0.2">
@@ -1409,7 +1448,7 @@
         <v>23</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C36" s="2"/>
     </row>
@@ -1418,10 +1457,10 @@
         <v>24</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="18" x14ac:dyDescent="0.2">
@@ -1429,405 +1468,456 @@
         <v>25</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="29" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="29" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="29" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="29" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="29" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="C46" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="163" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="168" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="C52" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="168" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="C53" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B54" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C54" s="6" t="s">
         <v>152</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="29" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B58" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="43" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C61" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B63" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="C63" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="51" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="C69" s="7" t="s">
         <v>181</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="187" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C70" s="7" t="s">
         <v>183</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="51" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>198</v>
+    </row>
+    <row r="77" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
